--- a/Test/Assets/Excel/EnemyData.xlsx
+++ b/Test/Assets/Excel/EnemyData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卒制\Graduation-Project\Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DAFD06-3EB0-4031-9920-F60D6C666DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED7FFE1-F279-4B2C-92F3-A50D38BCCC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
   </bookViews>
@@ -861,6 +861,9 @@
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4">
@@ -929,6 +932,9 @@
       <c r="V4">
         <v>0</v>
       </c>
+      <c r="W4" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5">
@@ -997,6 +1003,9 @@
       <c r="V5">
         <v>0</v>
       </c>
+      <c r="W5" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6">
@@ -1065,6 +1074,9 @@
       <c r="V6">
         <v>0</v>
       </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7">
@@ -1133,6 +1145,9 @@
       <c r="V7">
         <v>0</v>
       </c>
+      <c r="W7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8">
@@ -1201,6 +1216,9 @@
       <c r="V8">
         <v>0</v>
       </c>
+      <c r="W8" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9">
@@ -1269,6 +1287,9 @@
       <c r="V9">
         <v>0</v>
       </c>
+      <c r="W9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10">
@@ -1337,6 +1358,9 @@
       <c r="V10">
         <v>0</v>
       </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11">
@@ -1405,8 +1429,8 @@
       <c r="V11">
         <v>10</v>
       </c>
-      <c r="W11">
-        <v>5</v>
+      <c r="W11" s="1">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -1476,6 +1500,9 @@
       <c r="V12">
         <v>0</v>
       </c>
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13">
@@ -1542,6 +1569,9 @@
         <v>0</v>
       </c>
       <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1612,6 +1642,9 @@
       <c r="V14">
         <v>0</v>
       </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15">
@@ -1675,6 +1708,9 @@
         <v>0</v>
       </c>
       <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Test/Assets/Excel/EnemyData.xlsx
+++ b/Test/Assets/Excel/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\卒制\Graduation-Project\Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED7FFE1-F279-4B2C-92F3-A50D38BCCC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3518E676-5A7C-4E7A-95D4-91A27844C6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA82EEB-B8B9-4BF1-A7F3-81E7AF626BF5}"/>
   </bookViews>
@@ -1447,7 +1447,7 @@
         <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>0</v>
